--- a/backtest_runs/20260410_193731/by_symbol/QUICE/QUICE.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/QUICE/QUICE.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-4212.679999999991</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>95787.32000000001</v>
@@ -633,7 +633,7 @@
         <v>-5952.700000000003</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>94734.15000000001</v>
@@ -679,7 +679,7 @@
         <v>-10760.65000000001</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>83973.5</v>
@@ -817,7 +817,7 @@
         <v>-5036.899999999991</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>90475.68000000001</v>
@@ -863,7 +863,7 @@
         <v>-1098.960000000009</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>89376.72</v>
@@ -909,7 +909,7 @@
         <v>-3525.829999999998</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>85850.89</v>
@@ -955,7 +955,7 @@
         <v>-228.9500000000033</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>85621.94</v>
@@ -1047,7 +1047,7 @@
         <v>-1053.170000000002</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>87316.17</v>
@@ -1185,7 +1185,7 @@
         <v>-7692.719999999998</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>90887.79000000001</v>
@@ -1231,7 +1231,7 @@
         <v>-641.0600000000026</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>90246.73000000001</v>
@@ -1277,7 +1277,7 @@
         <v>-2152.129999999995</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>88094.60000000001</v>
@@ -1323,7 +1323,7 @@
         <v>-503.6900000000136</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>87590.91</v>
@@ -1415,7 +1415,7 @@
         <v>-4716.370000000005</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>86766.69</v>
@@ -1461,7 +1461,7 @@
         <v>-2793.189999999997</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>83973.5</v>
@@ -1553,7 +1553,7 @@
         <v>-1785.810000000003</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>91849.37999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-2976.349999999994</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>98488.93000000001</v>
